--- a/gte/nodes/P/compressor_blade_strength.xlsx
+++ b/gte/nodes/P/compressor_blade_strength.xlsx
@@ -1198,91 +1198,91 @@
         <v>2310.3654248608714</v>
       </c>
       <c r="G3">
-        <v>397.83760837372506</v>
+        <v>298.37820628029385</v>
       </c>
       <c r="H3">
-        <v>421398690.12439179</v>
+        <v>433083243.29319239</v>
       </c>
       <c r="I3">
-        <v>182394821870989.59</v>
+        <v>187452269945250.06</v>
       </c>
       <c r="J3">
-        <v>89.397764756258482</v>
+        <v>79.377079965523237</v>
       </c>
       <c r="K3">
-        <v>59.312763059530468</v>
+        <v>55.05256792507641</v>
       </c>
       <c r="L3">
-        <v>142.91829845374289</v>
+        <v>138.47294071061842</v>
       </c>
       <c r="M3">
-        <v>1.1197388624857805</v>
+        <v>1.0286625770690392</v>
       </c>
       <c r="N3">
-        <v>0.81776741769380012</v>
+        <v>0.775351957748007</v>
       </c>
       <c r="O3">
-        <v>1.5330310499855095</v>
+        <v>1.498804597221741</v>
       </c>
       <c r="P3">
-        <v>1.1197388624857805</v>
+        <v>1.0286625770690392</v>
       </c>
       <c r="Q3">
-        <v>0.81776741769380012</v>
+        <v>0.775351957748007</v>
       </c>
       <c r="R3">
-        <v>1.5330310499855095</v>
+        <v>1.498804597221741</v>
       </c>
       <c r="S3">
-        <v>142.68989460703892</v>
+        <v>165.58202271751952</v>
       </c>
       <c r="T3">
-        <v>228.03417823822338</v>
+        <v>179.14585077927848</v>
       </c>
       <c r="U3">
-        <v>137.85541612341035</v>
+        <v>134.62626742458468</v>
       </c>
       <c r="V3">
-        <v>8.736947578101262E-15</v>
+        <v>107.73440551488409</v>
       </c>
       <c r="W3">
-        <v>343.57000219576787</v>
+        <v>385.54468251886942</v>
       </c>
       <c r="X3">
-        <v>77.605062658285007</v>
+        <v>112.99329724268371</v>
       </c>
       <c r="Y3">
-        <v>63.458532650130032</v>
+        <v>63.458532650130017</v>
       </c>
       <c r="Z3">
-        <v>59.574570664650714</v>
+        <v>59.5745706646507</v>
       </c>
       <c r="AA3">
-        <v>21.05091942046273</v>
+        <v>16.59274454102453</v>
       </c>
       <c r="AB3">
-        <v>5.5365747425342757</v>
+        <v>5.1265717101464654</v>
       </c>
       <c r="AC3">
-        <v>2.7157890804616636</v>
+        <v>2.1646370289668289</v>
       </c>
       <c r="AD3">
-        <v>-7.04758229362116E-05</v>
+        <v>-6.5176743207926856E-05</v>
       </c>
       <c r="AE3">
-        <v>155148.9258848335</v>
+        <v>125891.73547776503</v>
       </c>
       <c r="AF3">
-        <v>1570.0054397850643</v>
+        <v>895.39312096982508</v>
       </c>
       <c r="AG3">
-        <v>2605106.9648732338</v>
+        <v>2603140.91751237</v>
       </c>
       <c r="AH3">
-        <v>307659.19435754517</v>
+        <v>230744.39576810965</v>
       </c>
       <c r="AI3">
-        <v>307659.19435754517</v>
+        <v>230744.39576810965</v>
       </c>
       <c r="AJ3">
         <v>49.178660381553357</v>
@@ -1297,136 +1297,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-15.26126256611402</v>
+        <v>-14.896407914701818</v>
       </c>
       <c r="AO3">
-        <v>-17.8724840402604</v>
+        <v>-17.872485018718589</v>
       </c>
       <c r="AP3">
-        <v>-20.35067137324484</v>
+        <v>-16.041538412801096</v>
       </c>
       <c r="AQ3">
-        <v>-5.53659672632211</v>
+        <v>-5.1265920409730379</v>
       </c>
       <c r="AR3">
-        <v>34556.856214674088</v>
+        <v>34624.369879950536</v>
       </c>
       <c r="AS3">
-        <v>5168.3526388115406</v>
+        <v>3873.9156647877394</v>
       </c>
       <c r="AT3">
-        <v>0.94437363762999438</v>
+        <v>1.1603615127071534</v>
       </c>
       <c r="AU3">
-        <v>-2.961243258770303</v>
+        <v>-3.3853213734682517</v>
       </c>
       <c r="AV3">
-        <v>-3.1515730043933954</v>
+        <v>-2.452400004955174</v>
       </c>
       <c r="AW3">
-        <v>2.2127576736525785</v>
+        <v>1.653750886949485</v>
       </c>
       <c r="AX3">
-        <v>368.18980669491225</v>
+        <v>210.16170051508655</v>
       </c>
       <c r="AY3">
-        <v>0.2930495533864077</v>
+        <v>0.22085031125849736</v>
       </c>
       <c r="AZ3">
-        <v>-175.25210317496212</v>
+        <v>-196.45679891862022</v>
       </c>
       <c r="BA3">
-        <v>0.38935410145124733</v>
+        <v>0.44345026121414172</v>
       </c>
       <c r="BB3">
-        <v>-0.019736097707220495</v>
+        <v>-0.020950499754575316</v>
       </c>
       <c r="BC3">
-        <v>-0.11836173946688336</v>
+        <v>-0.069008375060857441</v>
       </c>
       <c r="BD3">
-        <v>-35.622994168391394</v>
+        <v>-16.488896990146333</v>
       </c>
       <c r="BE3">
-        <v>0.9051066090112504</v>
+        <v>0.76249944445785056</v>
       </c>
       <c r="BF3">
-        <v>-1030851705580.3411</v>
+        <v>-476222297974.42</v>
       </c>
       <c r="BG3">
-        <v>175124778099.38663</v>
+        <v>196829128571.03449</v>
       </c>
       <c r="BH3">
-        <v>1.2123801789881037</v>
+        <v>-18.957554791819838</v>
       </c>
       <c r="BI3">
-        <v>39.374936963540208</v>
+        <v>48.9956114785456</v>
       </c>
       <c r="BJ3">
-        <v>364.39931956835096</v>
+        <v>262.5848768429891</v>
       </c>
       <c r="BK3">
-        <v>0.47353386864789937</v>
+        <v>0.479557482887043</v>
       </c>
       <c r="BL3">
-        <v>-183.00319483388066</v>
+        <v>-117.52615308133058</v>
       </c>
       <c r="BM3">
-        <v>0.11506664286505988</v>
+        <v>0.12428843373745269</v>
       </c>
       <c r="BN3">
-        <v>-1.7131583585455499</v>
+        <v>-1.2399928290232138</v>
       </c>
       <c r="BO3">
-        <v>0.071048033926576229</v>
+        <v>0.057622901256721044</v>
       </c>
       <c r="BP3">
-        <v>1.4724475459431403</v>
+        <v>1.432332842373931</v>
       </c>
       <c r="BQ3">
-        <v>16.912713042478327</v>
+        <v>15.855616580757122</v>
       </c>
       <c r="BR3">
-        <v>76.671772774812368</v>
+        <v>76.774128672861551</v>
       </c>
       <c r="BS3">
-        <v>-22.39597517510612</v>
+        <v>-17.834000503426303</v>
       </c>
       <c r="BT3">
-        <v>0.0046735352668742574</v>
+        <v>0.0030474207077420138</v>
       </c>
       <c r="BU3">
-        <v>3.91063445498475</v>
+        <v>3.2037030989117175</v>
       </c>
       <c r="BV3">
-        <v>59.567058748802808</v>
+        <v>59.568887149633476</v>
       </c>
       <c r="BW3">
-        <v>-5.8248382329613388</v>
+        <v>-5.3472665018501893</v>
       </c>
       <c r="BX3">
-        <v>39.826438495275518</v>
+        <v>33.1362985515619</v>
       </c>
       <c r="BY3">
-        <v>1.1794959884496226</v>
+        <v>1.715847808401552</v>
       </c>
       <c r="BZ3">
-        <v>-47.21554851457126</v>
+        <v>-33.731958374053782</v>
       </c>
       <c r="CA3">
-        <v>-1.7791247458638717</v>
+        <v>-2.8959921802546624</v>
       </c>
       <c r="CB3">
-        <v>222.22365133803891</v>
+        <v>220.58908254750457</v>
       </c>
       <c r="CC3">
-        <v>1.1924258780624948</v>
+        <v>1.7271002887645066</v>
       </c>
       <c r="CD3">
-        <v>1.0349933439358889</v>
+        <v>1.0426626619223949</v>
       </c>
       <c r="CE3">
-        <v>192.88410645172675</v>
+        <v>133.17118959231496</v>
       </c>
     </row>
   </sheetData>
@@ -2290,94 +2290,94 @@
         <v>156117997071144.72</v>
       </c>
       <c r="F3">
-        <v>1151.8711609832421</v>
+        <v>1202.4881253112892</v>
       </c>
       <c r="G3">
-        <v>779.70501885512442</v>
+        <v>649.75418237927056</v>
       </c>
       <c r="H3">
-        <v>149306921.82165766</v>
+        <v>154318570.22912282</v>
       </c>
       <c r="I3">
-        <v>129621199730539.84</v>
+        <v>128332718619715.47</v>
       </c>
       <c r="J3">
-        <v>89.397764756258482</v>
+        <v>85.67180670539507</v>
       </c>
       <c r="K3">
-        <v>108.29693022842736</v>
+        <v>110.18002365692928</v>
       </c>
       <c r="L3">
-        <v>148.41679033894022</v>
+        <v>146.14659000752067</v>
       </c>
       <c r="M3">
-        <v>1.1197388624857805</v>
+        <v>1.0862339043800009</v>
       </c>
       <c r="N3">
-        <v>1.2573783118239024</v>
+        <v>1.2729628157325739</v>
       </c>
       <c r="O3">
-        <v>1.574948670113445</v>
+        <v>1.5576965190223802</v>
       </c>
       <c r="P3">
-        <v>1.1197388624857805</v>
+        <v>1.0862339043800009</v>
       </c>
       <c r="Q3">
-        <v>1.2573783118239024</v>
+        <v>1.2729628157325739</v>
       </c>
       <c r="R3">
-        <v>1.574948670113445</v>
+        <v>1.5576965190223802</v>
       </c>
       <c r="S3">
         <v>142.68989460703892</v>
       </c>
       <c r="T3">
-        <v>125.36907725330042</v>
+        <v>112.87409573392633</v>
       </c>
       <c r="U3">
-        <v>99.2057416536664</v>
+        <v>112.87409573392633</v>
       </c>
       <c r="V3">
-        <v>8.736947578101262E-15</v>
+        <v>82.19755498559401</v>
       </c>
       <c r="W3">
-        <v>242.97269309595745</v>
+        <v>242.97269309595748</v>
       </c>
       <c r="X3">
-        <v>90.044501846578143</v>
+        <v>90.044501846578115</v>
       </c>
       <c r="Y3">
-        <v>82.768355519594635</v>
+        <v>74.7608880824119</v>
       </c>
       <c r="Z3">
-        <v>60.200378024019528</v>
+        <v>60.200378024019521</v>
       </c>
       <c r="AA3">
-        <v>9.0446186861291924</v>
+        <v>6.110503810833368</v>
       </c>
       <c r="AB3">
-        <v>4.5596839379318412</v>
+        <v>5.9165993076885632</v>
       </c>
       <c r="AC3">
-        <v>-8.3152048797150815E-05</v>
+        <v>0.6705340330422197</v>
       </c>
       <c r="AD3">
-        <v>0.62150719072452421</v>
+        <v>0.80479467253693349</v>
       </c>
       <c r="AE3">
-        <v>14621.639859171415</v>
+        <v>11403.810269462987</v>
       </c>
       <c r="AF3">
-        <v>4547.4216091755334</v>
+        <v>3870.4856814622713</v>
       </c>
       <c r="AG3">
-        <v>1719391.5132284924</v>
+        <v>1877861.8713289243</v>
       </c>
       <c r="AH3">
-        <v>789504.11351707752</v>
+        <v>657972.17451897252</v>
       </c>
       <c r="AI3">
-        <v>789504.11351707752</v>
+        <v>657972.17451897252</v>
       </c>
       <c r="AJ3">
         <v>57.9376826296774</v>
@@ -2392,136 +2392,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-24.83065976364373</v>
+        <v>-16.893563162188645</v>
       </c>
       <c r="AO3">
-        <v>-13.595362595219143</v>
+        <v>-13.628467412523639</v>
       </c>
       <c r="AP3">
-        <v>-9.0446547223049052</v>
+        <v>-5.91320743862986</v>
       </c>
       <c r="AQ3">
-        <v>-4.4124728111238971</v>
+        <v>-5.7257406633622177</v>
       </c>
       <c r="AR3">
-        <v>20826.217462190831</v>
+        <v>20765.54753807111</v>
       </c>
       <c r="AS3">
-        <v>10842.08170580196</v>
+        <v>9024.93345452698</v>
       </c>
       <c r="AT3">
-        <v>-1.6244731668561538</v>
+        <v>-1.8025023676501988</v>
       </c>
       <c r="AU3">
-        <v>-2.7996250500032347</v>
+        <v>-2.7813033621769252</v>
       </c>
       <c r="AV3">
-        <v>-3.9093016148164987</v>
+        <v>-2.2687191492240797</v>
       </c>
       <c r="AW3">
-        <v>1.8745518211822239</v>
+        <v>1.6971608520522612</v>
       </c>
       <c r="AX3">
-        <v>63.922837054661194</v>
+        <v>33.75776811725477</v>
       </c>
       <c r="AY3">
-        <v>64.494605229390814</v>
+        <v>51.735266680173332</v>
       </c>
       <c r="AZ3">
-        <v>-42.410153453688707</v>
+        <v>-48.214981990621219</v>
       </c>
       <c r="BA3">
-        <v>85.89676365166072</v>
+        <v>93.7907859416419</v>
       </c>
       <c r="BB3">
-        <v>-0.52701521093229042</v>
+        <v>-0.56993015434464356</v>
       </c>
       <c r="BC3">
-        <v>-2.1564877548697479</v>
+        <v>-1.1980568546115622</v>
       </c>
       <c r="BD3">
-        <v>-16.935071854790863</v>
+        <v>-7.1203415591463619</v>
       </c>
       <c r="BE3">
-        <v>-11.62790507509555</v>
+        <v>-10.620759785524303</v>
       </c>
       <c r="BF3">
-        <v>-813161193843.08813</v>
+        <v>-342892068995.15076</v>
       </c>
       <c r="BG3">
-        <v>-1072479011929.3297</v>
+        <v>-1176824165966.2148</v>
       </c>
       <c r="BH3">
-        <v>44.984030452085157</v>
+        <v>44.446561214132942</v>
       </c>
       <c r="BI3">
-        <v>49.470886252395736</v>
+        <v>48.010015768671416</v>
       </c>
       <c r="BJ3">
-        <v>15.232720570578678</v>
+        <v>-9.6624373735317768</v>
       </c>
       <c r="BK3">
-        <v>107.19886663059162</v>
+        <v>104.32203586625619</v>
       </c>
       <c r="BL3">
-        <v>-75.184535890706</v>
+        <v>-58.05952721661491</v>
       </c>
       <c r="BM3">
-        <v>6.7978748621060348</v>
+        <v>24.293253770112884</v>
       </c>
       <c r="BN3">
-        <v>-2.4034779320797983</v>
+        <v>2.0897923208272067</v>
       </c>
       <c r="BO3">
-        <v>0.02092745462983257</v>
+        <v>0.0784855906959382</v>
       </c>
       <c r="BP3">
-        <v>7.9634125570052365</v>
+        <v>-9.8787726634155622</v>
       </c>
       <c r="BQ3">
-        <v>7.63435720584832</v>
+        <v>6.9447323660610119</v>
       </c>
       <c r="BR3">
-        <v>-82.297483069085757</v>
+        <v>90.37575292038305</v>
       </c>
       <c r="BS3">
-        <v>-12.954334833664147</v>
+        <v>-10.474986675380791</v>
       </c>
       <c r="BT3">
-        <v>-0.15725615793833</v>
+        <v>-0.13894740561960761</v>
       </c>
       <c r="BU3">
-        <v>5.3362092390022573</v>
+        <v>5.0693593474113934</v>
       </c>
       <c r="BV3">
-        <v>73.040125017276324</v>
+        <v>72.995951417634245</v>
       </c>
       <c r="BW3">
-        <v>-5.3789745932606268</v>
+        <v>-7.0427080446789994</v>
       </c>
       <c r="BX3">
-        <v>8.3016385198525811</v>
+        <v>-6.1896958025419542</v>
       </c>
       <c r="BY3">
-        <v>125.79474458437021</v>
+        <v>136.64066664756334</v>
       </c>
       <c r="BZ3">
-        <v>-17.094389735221014</v>
+        <v>11.669673652532909</v>
       </c>
       <c r="CA3">
-        <v>-127.43041982994355</v>
+        <v>-192.51874253530215</v>
       </c>
       <c r="CB3">
-        <v>137.92523533484032</v>
+        <v>140.00281217505415</v>
       </c>
       <c r="CC3">
-        <v>125.799316279056</v>
+        <v>136.64573428032114</v>
       </c>
       <c r="CD3">
-        <v>1.6675701110216001</v>
+        <v>1.6428241435066089</v>
       </c>
       <c r="CE3">
-        <v>1.8283088239509937</v>
+        <v>1.6831846322269215</v>
       </c>
     </row>
   </sheetData>
@@ -3388,7 +3388,7 @@
         <v>701.28049855759764</v>
       </c>
       <c r="G3">
-        <v>1196.1212731936685</v>
+        <v>1046.60611404446</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -3397,49 +3397,49 @@
         <v>0</v>
       </c>
       <c r="J3">
-        <v>89.397764756258482</v>
+        <v>87.454020220708074</v>
       </c>
       <c r="K3">
-        <v>123.66330089121534</v>
+        <v>126.82795466049076</v>
       </c>
       <c r="L3">
-        <v>153.91386988478254</v>
+        <v>148.87340688986382</v>
       </c>
       <c r="M3">
-        <v>1.1197388624857805</v>
+        <v>1.1023111015231439</v>
       </c>
       <c r="N3">
-        <v>1.3824282940324093</v>
+        <v>1.407616575520388</v>
       </c>
       <c r="O3">
-        <v>1.6164146479156787</v>
+        <v>1.5784095533359244</v>
       </c>
       <c r="P3">
-        <v>1.1197388624857805</v>
+        <v>1.1023111015231439</v>
       </c>
       <c r="Q3">
-        <v>1.3824282940324093</v>
+        <v>1.407616575520388</v>
       </c>
       <c r="R3">
-        <v>1.6164146479156787</v>
+        <v>1.5784095533359244</v>
       </c>
       <c r="S3">
-        <v>142.68989460703892</v>
+        <v>136.68803610615922</v>
       </c>
       <c r="T3">
-        <v>88.147989118044023</v>
+        <v>90.268719536124649</v>
       </c>
       <c r="U3">
-        <v>52.358693353189913</v>
+        <v>105.07595415134018</v>
       </c>
       <c r="V3">
-        <v>8.736947578101262E-15</v>
+        <v>71.943319034385524</v>
       </c>
       <c r="W3">
-        <v>209.0179692467033</v>
+        <v>196.9086048023635</v>
       </c>
       <c r="X3">
-        <v>91.204060836546546</v>
+        <v>79.5589226239994</v>
       </c>
       <c r="Y3">
         <v>91.332059899452346</v>
@@ -3448,31 +3448,31 @@
         <v>64.573197552003322</v>
       </c>
       <c r="AA3">
-        <v>1.1202722503377751</v>
+        <v>0.12406047088604852</v>
       </c>
       <c r="AB3">
-        <v>1.6643180116297429</v>
+        <v>6.7688620846223593</v>
       </c>
       <c r="AC3">
-        <v>-9.2635784253528109E-06</v>
+        <v>-1.0258003219098082E-06</v>
       </c>
       <c r="AD3">
-        <v>0.21233415642723336</v>
+        <v>0.86018386176663741</v>
       </c>
       <c r="AE3">
-        <v>1292.0447607837082</v>
+        <v>1216.4029719148273</v>
       </c>
       <c r="AF3">
-        <v>9828.61202023126</v>
+        <v>10826.639924143785</v>
       </c>
       <c r="AG3">
-        <v>1274619.294468818</v>
+        <v>1274619.2944687852</v>
       </c>
       <c r="AH3">
-        <v>1393582.3865111182</v>
+        <v>1219640.3951969293</v>
       </c>
       <c r="AI3">
-        <v>1393582.3865111182</v>
+        <v>1219640.3951969293</v>
       </c>
       <c r="AJ3">
         <v>63.932258496019372</v>
@@ -3487,136 +3487,136 @@
         <v>0</v>
       </c>
       <c r="AN3">
-        <v>-27.399801222307069</v>
+        <v>-27.39980140121185</v>
       </c>
       <c r="AO3">
-        <v>-14.536769825518778</v>
+        <v>-14.63068164185658</v>
       </c>
       <c r="AP3">
-        <v>-1.1202766803361179</v>
+        <v>-0.12406096144094349</v>
       </c>
       <c r="AQ3">
-        <v>-1.6104569403775919</v>
+        <v>-6.54995745698912</v>
       </c>
       <c r="AR3">
-        <v>13968.976164157424</v>
+        <v>13969.18586773903</v>
       </c>
       <c r="AS3">
-        <v>17895.395056927144</v>
+        <v>15635.500601707221</v>
       </c>
       <c r="AT3">
-        <v>-3.3299892961054125</v>
+        <v>-3.8082523534512527</v>
       </c>
       <c r="AU3">
-        <v>-2.6008491123788193</v>
+        <v>-2.4037027671142588</v>
       </c>
       <c r="AV3">
-        <v>-4.3523835867211469</v>
+        <v>-2.2144991112942378</v>
       </c>
       <c r="AW3">
-        <v>1.4422669278882032</v>
+        <v>1.4979510785885795</v>
       </c>
       <c r="AX3">
         <v>0</v>
       </c>
       <c r="AY3">
-        <v>181.72248752688773</v>
+        <v>151.62082213036479</v>
       </c>
       <c r="AZ3">
         <v>0</v>
       </c>
       <c r="BA3">
-        <v>251.13586495978512</v>
+        <v>266.1618040080719</v>
       </c>
       <c r="BB3">
-        <v>-1.1633662406503305</v>
+        <v>-1.280691417783927</v>
       </c>
       <c r="BC3">
-        <v>-3.9031898121232018</v>
+        <v>-2.1202565674145073</v>
       </c>
       <c r="BD3">
         <v>0</v>
       </c>
       <c r="BE3">
-        <v>-17.060802173634823</v>
+        <v>-17.21786580371009</v>
       </c>
       <c r="BF3">
         <v>0</v>
       </c>
       <c r="BG3">
-        <v>-953362701374.43774</v>
+        <v>-1101203360372.7463</v>
       </c>
       <c r="BH3">
-        <v>68.601247771010136</v>
+        <v>68.2021241263469</v>
       </c>
       <c r="BI3">
-        <v>62.605051507807573</v>
+        <v>46.891629332270128</v>
       </c>
       <c r="BJ3">
         <v>0</v>
       </c>
       <c r="BK3">
-        <v>306.58689838353291</v>
+        <v>297.92944165773184</v>
       </c>
       <c r="BL3">
         <v>0</v>
       </c>
       <c r="BM3">
-        <v>-45.79037979340832</v>
+        <v>71.1971025381731</v>
       </c>
       <c r="BN3">
         <v>90</v>
       </c>
       <c r="BO3">
-        <v>-0.060353528923793573</v>
+        <v>0.1215437890683688</v>
       </c>
       <c r="BP3">
-        <v>-0.87369116270117686</v>
+        <v>0.1225337481408449</v>
       </c>
       <c r="BQ3">
-        <v>91.332059758195214</v>
+        <v>91.332059901646147</v>
       </c>
       <c r="BR3">
-        <v>-1.3668533380590806</v>
+        <v>-0.37065468992232453</v>
       </c>
       <c r="BS3">
-        <v>-91.331536024454124</v>
+        <v>-91.331535810096227</v>
       </c>
       <c r="BT3">
-        <v>-3.07597046534157</v>
+        <v>-0.11320670371982952</v>
       </c>
       <c r="BU3">
-        <v>6.2043409788201691</v>
+        <v>6.9837139477866783</v>
       </c>
       <c r="BV3">
-        <v>-25.98349042524821</v>
+        <v>78.277878116852634</v>
       </c>
       <c r="BW3">
-        <v>-5.4334282292291531</v>
+        <v>-8.1112300022905082</v>
       </c>
       <c r="BX3">
         <v>0</v>
       </c>
       <c r="BY3">
-        <v>193.43283385957813</v>
+        <v>192.18571593329168</v>
       </c>
       <c r="BZ3">
         <v>0</v>
       </c>
       <c r="CA3">
-        <v>-170.34035367274393</v>
+        <v>-227.77580807315263</v>
       </c>
       <c r="CB3">
         <v>0</v>
       </c>
       <c r="CC3">
-        <v>193.43518324076291</v>
+        <v>192.18887079545675</v>
       </c>
       <c r="CD3">
         <v>1E+307</v>
       </c>
       <c r="CE3">
-        <v>1.189028780321344</v>
+        <v>1.19673943162289</v>
       </c>
     </row>
   </sheetData>
